--- a/AtchisonRegime/Outputs/China/ASX300_Materials/df_regEquityReturns_ASX300_Materials.xlsx
+++ b/AtchisonRegime/Outputs/China/ASX300_Materials/df_regEquityReturns_ASX300_Materials.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5602,7 +5602,7 @@
         <v>-0.7573208650167998</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.2748089633951488</v>
+        <v>-0.3947190755637957</v>
       </c>
       <c r="D91" t="b">
         <v>0</v>
@@ -5659,7 +5659,7 @@
         <v>-0.6936456221255526</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.2279126352522796</v>
+        <v>-0.2155123505395301</v>
       </c>
       <c r="D92" t="b">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>-0.6126315461159145</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.1571771349177754</v>
+        <v>-0.1369821570201432</v>
       </c>
       <c r="D93" t="b">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>-0.5084519801903494</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.05568094083677352</v>
+        <v>-0.03027941206202257</v>
       </c>
       <c r="D94" t="b">
         <v>0</v>
@@ -5830,7 +5830,7 @@
         <v>-0.4336219428364395</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06489742026200002</v>
+        <v>0.09304350422744435</v>
       </c>
       <c r="D95" t="b">
         <v>0</v>
@@ -5887,7 +5887,7 @@
         <v>-0.4657215735652193</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1759128359355281</v>
+        <v>0.2054174209692945</v>
       </c>
       <c r="D96" t="b">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>-0.5505039986564023</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2313892661628568</v>
+        <v>0.2757055266963961</v>
       </c>
       <c r="D97" t="b">
         <v>0</v>
@@ -6001,7 +6001,7 @@
         <v>-0.6105568779169617</v>
       </c>
       <c r="C98" t="n">
-        <v>0.277805270977266</v>
+        <v>0.3123296962227394</v>
       </c>
       <c r="D98" t="b">
         <v>0</v>
@@ -6058,7 +6058,7 @@
         <v>-0.5325494453957975</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2780095875200979</v>
+        <v>0.3223443003377225</v>
       </c>
       <c r="D99" t="b">
         <v>0</v>
@@ -6115,7 +6115,7 @@
         <v>-0.7633229331216338</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2782716760091419</v>
+        <v>0.3213732415420884</v>
       </c>
       <c r="D100" t="b">
         <v>0</v>
@@ -6169,10 +6169,10 @@
         <v>45747</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.9436146564825021</v>
+        <v>-0.7835479487520001</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2879412727724567</v>
+        <v>0.3105360517581144</v>
       </c>
       <c r="D101" t="b">
         <v>0</v>
@@ -6218,6 +6218,63 @@
         <v>120.6273124223395</v>
       </c>
       <c r="Q101" t="n">
+        <v>130.8510474984139</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B102" t="n">
+        <v>-0.9346642881743581</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.2967768877878058</v>
+      </c>
+      <c r="D102" t="b">
+        <v>0</v>
+      </c>
+      <c r="E102" t="b">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-0.132402670757728</v>
+      </c>
+      <c r="G102" t="n">
+        <v>248397.4621502019</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>-0.132402670757728</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
+        <v>111.5015954503959</v>
+      </c>
+      <c r="O102" t="n">
+        <v>135.937670794123</v>
+      </c>
+      <c r="P102" t="n">
+        <v>120.6273124223395</v>
+      </c>
+      <c r="Q102" t="n">
         <v>130.8510474984139</v>
       </c>
     </row>
